--- a/German Bundesliga/Raw/25_26.xlsx
+++ b/German Bundesliga/Raw/25_26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AP28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3086,6 +3086,1230 @@
       </c>
       <c r="AP19" t="n">
         <v>81.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>472</v>
+      </c>
+      <c r="L20" t="n">
+        <v>25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>26</v>
+      </c>
+      <c r="O20" t="n">
+        <v>31</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>16</v>
+      </c>
+      <c r="R20" t="n">
+        <v>19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>59</v>
+      </c>
+      <c r="T20" t="n">
+        <v>345</v>
+      </c>
+      <c r="U20" t="n">
+        <v>264</v>
+      </c>
+      <c r="V20" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>644</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>526</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>440</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>43</v>
+      </c>
+      <c r="H21" t="n">
+        <v>13</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26</v>
+      </c>
+      <c r="K21" t="n">
+        <v>523</v>
+      </c>
+      <c r="L21" t="n">
+        <v>15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" t="n">
+        <v>25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>34</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>30</v>
+      </c>
+      <c r="S21" t="n">
+        <v>72</v>
+      </c>
+      <c r="T21" t="n">
+        <v>386</v>
+      </c>
+      <c r="U21" t="n">
+        <v>259</v>
+      </c>
+      <c r="V21" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>57</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>671</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>505</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>385</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>31</v>
+      </c>
+      <c r="K22" t="n">
+        <v>519</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>20</v>
+      </c>
+      <c r="O22" t="n">
+        <v>20</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>23</v>
+      </c>
+      <c r="S22" t="n">
+        <v>77</v>
+      </c>
+      <c r="T22" t="n">
+        <v>419</v>
+      </c>
+      <c r="U22" t="n">
+        <v>294</v>
+      </c>
+      <c r="V22" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>54</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>633</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>62</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>71</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>488</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>398</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>81.59999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>55</v>
+      </c>
+      <c r="H23" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>21</v>
+      </c>
+      <c r="K23" t="n">
+        <v>599</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>11</v>
+      </c>
+      <c r="O23" t="n">
+        <v>34</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>14</v>
+      </c>
+      <c r="S23" t="n">
+        <v>62</v>
+      </c>
+      <c r="T23" t="n">
+        <v>490</v>
+      </c>
+      <c r="U23" t="n">
+        <v>412</v>
+      </c>
+      <c r="V23" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>490</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>67</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>405</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>314</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mainz 05</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>56</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>632</v>
+      </c>
+      <c r="L24" t="n">
+        <v>14</v>
+      </c>
+      <c r="M24" t="n">
+        <v>13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>21</v>
+      </c>
+      <c r="O24" t="n">
+        <v>19</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>23</v>
+      </c>
+      <c r="S24" t="n">
+        <v>93</v>
+      </c>
+      <c r="T24" t="n">
+        <v>506</v>
+      </c>
+      <c r="U24" t="n">
+        <v>360</v>
+      </c>
+      <c r="V24" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>578</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>63</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>67</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>395</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>277</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>70.09999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>25</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>399</v>
+      </c>
+      <c r="L25" t="n">
+        <v>11</v>
+      </c>
+      <c r="M25" t="n">
+        <v>19</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>34</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>11</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7</v>
+      </c>
+      <c r="S25" t="n">
+        <v>68</v>
+      </c>
+      <c r="T25" t="n">
+        <v>273</v>
+      </c>
+      <c r="U25" t="n">
+        <v>188</v>
+      </c>
+      <c r="V25" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>937</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>836</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>741</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>88.59999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11</v>
+      </c>
+      <c r="G26" t="n">
+        <v>70</v>
+      </c>
+      <c r="H26" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>17</v>
+      </c>
+      <c r="K26" t="n">
+        <v>898</v>
+      </c>
+      <c r="L26" t="n">
+        <v>8</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>17</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>16</v>
+      </c>
+      <c r="S26" t="n">
+        <v>31</v>
+      </c>
+      <c r="T26" t="n">
+        <v>809</v>
+      </c>
+      <c r="U26" t="n">
+        <v>735</v>
+      </c>
+      <c r="V26" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>454</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>350</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>285</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>81.40000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>56</v>
+      </c>
+      <c r="H27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>17</v>
+      </c>
+      <c r="K27" t="n">
+        <v>705</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6</v>
+      </c>
+      <c r="N27" t="n">
+        <v>21</v>
+      </c>
+      <c r="O27" t="n">
+        <v>27</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>20</v>
+      </c>
+      <c r="S27" t="n">
+        <v>73</v>
+      </c>
+      <c r="T27" t="n">
+        <v>587</v>
+      </c>
+      <c r="U27" t="n">
+        <v>466</v>
+      </c>
+      <c r="V27" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>610</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>458</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>364</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>55</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>28</v>
+      </c>
+      <c r="K28" t="n">
+        <v>677</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20</v>
+      </c>
+      <c r="M28" t="n">
+        <v>7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" t="n">
+        <v>21</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>14</v>
+      </c>
+      <c r="S28" t="n">
+        <v>52</v>
+      </c>
+      <c r="T28" t="n">
+        <v>554</v>
+      </c>
+      <c r="U28" t="n">
+        <v>452</v>
+      </c>
+      <c r="V28" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>597</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>461</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>374</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>81.09999999999999</v>
       </c>
     </row>
   </sheetData>
